--- a/artfynd/A 27488-2023 artfynd.xlsx
+++ b/artfynd/A 27488-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27488-2023 artfynd.xlsx
+++ b/artfynd/A 27488-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104731836</v>
+        <v>104732043</v>
       </c>
       <c r="B2" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574797.9804747993</v>
+        <v>574727</v>
       </c>
       <c r="R2" t="n">
-        <v>6659326.526959565</v>
+        <v>6659212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +746,14 @@
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,16 +765,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Under tall</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Kollekt nr. 1996</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -813,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104731795</v>
+        <v>104760436</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,26 +796,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -864,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574784</v>
+        <v>574755</v>
       </c>
       <c r="R3" t="n">
-        <v>6659317</v>
+        <v>6659304</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,12 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fjolårex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,19 +880,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Patrick Fritzson, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -931,19 +902,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104732043</v>
+        <v>104821648</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,8 +930,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -974,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574727.2585205527</v>
+        <v>574604</v>
       </c>
       <c r="R4" t="n">
-        <v>6659212.726378611</v>
+        <v>6659277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,27 +978,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fjolårsexemplar</t>
+          <t>Fyra årsfärska, tre gamla frk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104693643</v>
+        <v>104821671</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,26 +1031,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574895</v>
+        <v>574665</v>
       </c>
       <c r="R5" t="n">
-        <v>6659296</v>
+        <v>6659276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,12 +1096,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fjolårets frk, fem st</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,13 +1115,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1173,42 +1138,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104821648</v>
+        <v>104693643</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574603.394058679</v>
+        <v>574895</v>
       </c>
       <c r="R6" t="n">
-        <v>6659277.132423651</v>
+        <v>6659296</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,27 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fyra årsfärska, tre gamla frk</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,19 +1228,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Patrick Fritzson, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1306,42 +1250,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104760441</v>
+        <v>104731795</v>
       </c>
       <c r="B7" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574747.4519575123</v>
+        <v>574784</v>
       </c>
       <c r="R7" t="n">
-        <v>6659277.558792265</v>
+        <v>6659317</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,22 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,18 +1340,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrick Fritzson, Björn Bråvander</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1433,42 +1363,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104760436</v>
+        <v>104821593</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1484,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574754.9250430277</v>
+        <v>574429</v>
       </c>
       <c r="R8" t="n">
-        <v>6659303.678959765</v>
+        <v>6659146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,44 +1442,30 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fjolårex</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrick Fritzson, Björn Bråvander</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1565,15 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104821604</v>
+        <v>104693624</v>
       </c>
       <c r="B9" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,26 +1487,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>256703</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1616,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574490.1663650541</v>
+        <v>574684</v>
       </c>
       <c r="R9" t="n">
-        <v>6659236.385290748</v>
+        <v>6659154</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,22 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,19 +1566,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Patrick Fritzson, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1693,15 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104821671</v>
+        <v>104731948</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,34 +1599,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1744,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574664.447760225</v>
+        <v>574948</v>
       </c>
       <c r="R10" t="n">
-        <v>6659275.873719431</v>
+        <v>6659244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1774,27 +1657,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårets frk, fem st</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,50 +1694,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104821593</v>
+        <v>104760443</v>
       </c>
       <c r="B11" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1877,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574428.9697359954</v>
+        <v>574947</v>
       </c>
       <c r="R11" t="n">
-        <v>6659145.753899717</v>
+        <v>6659266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,40 +1766,29 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Patrick Fritzson, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1954,15 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104821672</v>
+        <v>110635195</v>
       </c>
       <c r="B12" t="n">
-        <v>88911</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,48 +1810,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långheden - Rosshyttan, Vstm</t>
+          <t>Rosshyttan, SV, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574748.6142448285</v>
+        <v>574908</v>
       </c>
       <c r="R12" t="n">
-        <v>6659269.592099022</v>
+        <v>6659294</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2035,22 +1864,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett stort bestånd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,48 +1887,34 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>Kollekt nr. 4938</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre, mager tallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
-        </is>
-      </c>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>104693860</v>
       </c>
       <c r="B13" t="n">
-        <v>89839</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2225,53 +2035,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110635195</v>
+        <v>104731836</v>
       </c>
       <c r="B14" t="n">
-        <v>95539</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224358</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rosshyttan, SV, Vstm</t>
+          <t>Långheden - Rosshyttan, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574908.1958278675</v>
+        <v>574798</v>
       </c>
       <c r="R14" t="n">
-        <v>6659293.811608107</v>
+        <v>6659326</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2295,27 +2111,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett stort bestånd.</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2330,21 +2131,388 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>äldre, mager tallskog</t>
+          <t>Under tall</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Kollekt nr. 1996</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Björn Bråvander, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104760441</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långheden - Rosshyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574747</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659278</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson, Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104821604</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långheden - Rosshyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574490</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659237</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104821672</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långheden - Rosshyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>574748</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6659270</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Kollekt nr. 4938</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27488-2023 artfynd.xlsx
+++ b/artfynd/A 27488-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104732043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104760436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821648</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104693643</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731795</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821593</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1583,6 +1623,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104693624</t>
         </is>
       </c>
     </row>
@@ -1691,6 +1736,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731948</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104760443</t>
         </is>
       </c>
     </row>
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110635195</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden, Fynd med DNA-sekvens - 1</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104693860</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2155,6 +2220,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731836</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2267,6 +2337,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104760441</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2380,6 +2455,11 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821604</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2513,8 +2593,31 @@
           <t>Inventering av marksvampar i potentiellt värdefulla skogsområden</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>